--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 DEER BUCK DRAW.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 DEER BUCK DRAW.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$460</definedName>
@@ -1218,7 +1218,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t>10.3</t>
@@ -1425,7 +1429,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -1563,7 +1571,11 @@
           <t>90.0</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
           <t>5.6</t>
@@ -1701,7 +1713,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>11.0</t>
@@ -1770,7 +1786,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t>22.0</t>
@@ -1908,7 +1928,11 @@
           <t>92.9</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -4587,7 +4611,11 @@
           <t>37.0</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
           <t>8.3</t>
@@ -4725,7 +4753,11 @@
           <t>88.9</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
           <t>7.2</t>
@@ -4794,7 +4826,11 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="N66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
           <t>6.3</t>
@@ -22918,7 +22954,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N346" s="3" t="inlineStr"/>
+      <c r="N346" s="3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O346" s="3" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -22975,7 +23015,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N347" s="5" t="inlineStr"/>
+      <c r="N347" s="5" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O347" s="5" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -23032,7 +23076,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N348" s="3" t="inlineStr"/>
+      <c r="N348" s="3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O348" s="3" t="inlineStr">
         <is>
           <t>6.0</t>
